--- a/uda/attachments/object-access/ObjectAccessTemplate.xlsx
+++ b/uda/attachments/object-access/ObjectAccessTemplate.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DTB_FINANCE_ANALYTICS</t>
+          <t>Manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -519,9 +519,6 @@
           <t>fin_prd</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>USE_CATALOG</t>
@@ -561,7 +558,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DTB_FINANCE_ANALYTICS</t>
+          <t>Manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -579,8 +576,6 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>USE_SCHEMA</t>
@@ -591,7 +586,6 @@
           <t>Finance reporting</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -616,7 +610,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DTB_FINANCE_ANALYTICS</t>
+          <t>Manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -639,7 +633,6 @@
           <t>v_monthly_close</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>SELECT</t>
@@ -679,7 +672,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DTB_FINANCE_ANALYTICS</t>
+          <t>Manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,9 +680,6 @@
           <t>FOLDER</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>/Volumes/prd/raw/finance</t>

--- a/uda/attachments/object-access/ObjectAccessTemplate.xlsx
+++ b/uda/attachments/object-access/ObjectAccessTemplate.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manoj@54legacy.com</t>
+          <t>manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manoj@54legacy.com</t>
+          <t>manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manoj@54legacy.com</t>
+          <t>manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manoj@54legacy.com</t>
+          <t>manoj@54legacy.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
